--- a/Lasser_Driver_v5/CH_Card/CH_Card_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/CH_Card/CH_Card_BOM_digikey_priced.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>118162</v>
+        <v>117162</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1988</v>
+        <v>1968</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3418056</v>
+        <v>3413350</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>197539</v>
+        <v>197469</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R56,R57,R58,R59,R68,R69,R70,R73,R74,R75,R76</t>
+          <t>CH_Card R56,R57,R58,R59,R69,R70,R75</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Res 47R 1% (gate/protection)</t>
+          <t>Res 47R 1% (gate resistors + NTC/monitor line protection)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>224802</v>
+        <v>224752</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.034</v>
+        <v>0.1</v>
       </c>
       <c r="O22" s="4">
         <f>N22*L22</f>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>860934</v>
+        <v>855984</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>RC0805FR-07100KL</t>
+          <t>RC0805FR-072KL</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R_bias1</t>
+          <t>CH_Card R77</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>2k</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Res 100k 1% (PD bias)</t>
+          <t>Res 2k 1% (trim)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>311-100KCRTR-ND</t>
+          <t>311-2.00KCRTR-ND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>760267</v>
+        <v>249333</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2435,22 +2435,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>RC0805FR-072KL</t>
+          <t>ERA-6AEB103V</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>Panasonic Industry</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R77</t>
+          <t>CH_Card R_NTC1</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2k</t>
+          <t>10k 0.1%</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2460,21 +2460,21 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Res 2k 1% (trim)</t>
+          <t>Res 10k 0.1% (NTC pullup; same as pm1p8V)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>311-2.00KCRTR-ND</t>
+          <t>P10KDATR-ND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>Panasonic Industry</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>249333</v>
+        <v>170424</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2496,18 +2496,18 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
+          <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDM0000/AOA0000C307.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ERA-6AEB103V</t>
+          <t>ERA-6AEB203V</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R_NTC1</t>
+          <t>CH_Card R43,R45,R_bias1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10k 0.1%</t>
+          <t>20k 0.1%</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Res 10k 0.1% (NTC pullup; same as pm1p8V)</t>
+          <t>Res 20k 0.1% (TEC scaler bottom R43/R45; PD monitor bias R_bias1)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P10KDATR-ND</t>
+          <t>P20KDATR-ND</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>170474</v>
+        <v>108045</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
@@ -2575,11 +2575,11 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ERA-6AEB203V</t>
+          <t>ERA-6AEB204V</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R43,R45</t>
+          <t>CH_Card R66</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20k 0.1%</t>
+          <t>200k 0.1%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Res 20k 0.1% (TEC scaler bottom)</t>
+          <t>Res 200k 0.1% (laser scaler top)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P20KDATR-ND</t>
+          <t>P200KDATR-ND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>108045</v>
+        <v>384782</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
@@ -2647,26 +2647,26 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ERA-6AEB204V</t>
+          <t>TNPW08054K99BEEA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Panasonic Industry</t>
+          <t>Vishay Dale</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R66</t>
+          <t>CH_Card R44,R117,R118,R119</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>200k 0.1%</t>
+          <t>4.99k 0.1%</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2676,21 +2676,21 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Res 200k 0.1% (laser scaler top)</t>
+          <t>Res 4.99k 0.1% (TEC scaler top, VZERO trim, ADC prot) - ERA-6AEB4991V 0 stock</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P200KDATR-ND</t>
+          <t>TNP4.99KABTR-ND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Panasonic Industry</t>
+          <t>Vishay Dale</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>384782</v>
+        <v>23385</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2698,13 +2698,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="O31" s="4">
         <f>N31*L31</f>
@@ -2712,18 +2712,18 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDM0000/AOA0000C307.pdf</t>
+          <t>https://www.vishay.com/docs/28758/tnpw_e3.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TNPW08054K99BEEA</t>
+          <t>TNPW08051K00BEEA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R44,R117,R118,R119</t>
+          <t>CH_Card R67</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4.99k 0.1%</t>
+          <t>1k 0.1%</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Res 4.99k 0.1% (TEC scaler top, VZERO trim, ADC prot) - ERA-6AEB4991V 0 stock</t>
+          <t>Res 1k 0.1% (laser scaler bottom) - ERA-6AEB102V 0 stock</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TNP4.99KABTR-ND</t>
+          <t>TNP1.00KABTR-ND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>23385</v>
+        <v>19030</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
@@ -2791,50 +2791,50 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TNPW08051K00BEEA</t>
+          <t>CL21B104KBCNNNC</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Vishay Dale</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CH_Card R67</t>
+          <t>CH_Card C65,C66,C_NTC1,C116,C117,C118,C122,C123,C130,C131,C132,C133,C134,C135,C136,C137,C138,C139,C140,C141,C142,C143,C144,C145,C146,C147,C148,C149,C152,C153,C155,C156,C158,C161,C164,C165,C166</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1k 0.1%</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>R_0805</t>
+          <t>C_0805</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Res 1k 0.1% (laser scaler bottom) - ERA-6AEB102V 0 stock</t>
+          <t>MLCC 100nF 50V X7R (decoupling bank + misc; same as pm1p8V)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>TNP1.00KABTR-ND</t>
+          <t>1276-1003-2-ND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Vishay Dale</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>19030</v>
+        <v>7390781</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.41</v>
+        <v>0.038</v>
       </c>
       <c r="O33" s="4">
         <f>N33*L33</f>
@@ -2856,33 +2856,33 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.vishay.com/docs/28758/tnpw_e3.pdf</t>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21B104KBCNNN_Spec.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CL21B104KBCNNNC</t>
+          <t>C0805C105K5RACTU</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>KEMET</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C65,C66,C_NTC1,C116,C117,C118,C122,C123,C130,C131,C132,C133,C134,C135,C136,C137,C138,C139,C140,C141,C142,C143,C144,C145,C146,C147,C148,C149,C152,C153,C155,C156,C158,C161,C164,C165,C166</t>
+          <t>CH_Card C113,C114</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2892,21 +2892,21 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>MLCC 100nF 50V X7R (decoupling bank + misc; same as pm1p8V)</t>
+          <t>MLCC 1uF 50V X7R (DAC output filters; same as pm1p8V)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1276-1003-2-ND</t>
+          <t>399-C0805C105K5RACTUTR-ND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>KEMET</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7506957</v>
+        <v>139665</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.038</v>
+        <v>0.87</v>
       </c>
       <c r="O34" s="4">
         <f>N34*L34</f>
@@ -2928,18 +2928,18 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21B104KBCNNN_Spec.pdf</t>
+          <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1002_X7R_SMD</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C0805C105K5RACTU</t>
+          <t>C0805C106K3PACTU</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C113,C114</t>
+          <t>CH_Card C115,C121,C150,C151,C154,C157,C160,C163</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>MLCC 1uF 50V X7R (DAC output filters; same as pm1p8V)</t>
+          <t>MLCC 10uF 25V X5R (rail bulk; same as pm1p8V)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>399-C0805C105K5RACTUTR-ND</t>
+          <t>399-11939-2-ND</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>144665</v>
+        <v>212636</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.87</v>
+        <v>0.24</v>
       </c>
       <c r="O35" s="4">
         <f>N35*L35</f>
@@ -3000,57 +3000,57 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1002_X7R_SMD</t>
+          <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1006_X5R_SMD</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C0805C106K3PACTU</t>
+          <t>1210YD107MAT2A</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KEMET</t>
+          <t>KYOCERA AVX</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C115,C121,C150,C151,C154,C157,C160,C163</t>
+          <t>CH_Card C159,C162</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>100uF</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>C_0805</t>
+          <t>C_1210</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>MLCC 10uF 25V X5R (rail bulk; same as pm1p8V)</t>
+          <t>MLCC 100uF 16V X5R (+/-6V_TEC bulk; same as pm1p8V)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>399-11939-2-ND</t>
+          <t>478-11408-2-ND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>KEMET</t>
+          <t>KYOCERA AVX</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>215140</v>
+        <v>4559</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.24</v>
+        <v>2.45</v>
       </c>
       <c r="O36" s="4">
         <f>N36*L36</f>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1006_X5R_SMD</t>
+          <t>https://datasheets.kyocera-avx.com/cx5r.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
@@ -3083,46 +3083,46 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1210YD107MAT2A</t>
+          <t>CL21B103KBANNNC</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>KYOCERA AVX</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C159,C162</t>
+          <t>CH_Card C119,C120</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100uF</t>
+          <t>10nF</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>C_1210</t>
+          <t>C_0805</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>MLCC 100uF 16V X5R (+/-6V_TEC bulk; same as pm1p8V)</t>
+          <t>MLCC 10nF 50V X7R (ADC input filters)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>478-11408-2-ND</t>
+          <t>1276-1015-2-ND</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>KYOCERA AVX</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>4559</v>
+        <v>2434788</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>2.45</v>
+        <v>0.1</v>
       </c>
       <c r="O37" s="4">
         <f>N37*L37</f>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://datasheets.kyocera-avx.com/cx5r.pdf</t>
+          <t>https://www.samsungsem.com/kr/support/product-search/mlcc/CL21B103KBANNNC.jsp</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CL21B103KBANNNC</t>
+          <t>C0805C103J5GACTU</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>KEMET</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C119,C120</t>
+          <t>CH_Card C70</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10nF</t>
+          <t>10nF C0G</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3180,21 +3180,21 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>MLCC 10nF 50V X7R (ADC input filters)</t>
+          <t>MLCC 10nF 50V C0G (laser filter)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1276-1015-2-ND</t>
+          <t>399-C0805C103J5GACTUTR-ND</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>KEMET</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2434688</v>
+        <v>40958</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="O38" s="4">
         <f>N38*L38</f>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://www.samsungsem.com/kr/support/product-search/mlcc/CL21B103KBANNNC.jsp</t>
+          <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1003_C0G_SMD</t>
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C0805C103J5GACTU</t>
+          <t>CL21B102KBANNNC</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>KEMET</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C70</t>
+          <t>CH_Card C76</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10nF C0G</t>
+          <t>1nF</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3252,21 +3252,21 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>MLCC 10nF 50V C0G (laser filter)</t>
+          <t>MLCC 1nF 50V X7R (lock integrator Ci)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>399-C0805C103J5GACTUTR-ND</t>
+          <t>1276-1020-2-ND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>KEMET</t>
+          <t>Samsung Electro-Mechanics</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>40958</v>
+        <v>1394498</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.65</v>
+        <v>0.1</v>
       </c>
       <c r="O39" s="4">
         <f>N39*L39</f>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://yageogroup.com/content/datasheet/asset/file/KEM_C1003_C0G_SMD</t>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8923/DataSheet_CL21B102KBANNN_20260513.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CL21B102KBANNNC</t>
+          <t>CL21C101JBANNNC</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C76</t>
+          <t>CH_Card C68</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1nF</t>
+          <t>100pF NP0</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MLCC 1nF 50V X7R (lock integrator Ci)</t>
+          <t>MLCC 100pF 50V C0G (comp)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1276-1020-2-ND</t>
+          <t>1276-1014-2-ND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1394604</v>
+        <v>188189</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3360,57 +3360,57 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8923/DataSheet_CL21B102KBANNN_20260513.pdf</t>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21C101JBANNNC_Spec.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CL21C101JBANNNC</t>
+          <t>GRM1555C1H2R2CA01D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>Murata Electronics</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C68</t>
+          <t>CH_Card C_f1,C_f2</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>100pF NP0</t>
+          <t>2.2pF</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>C_0805</t>
+          <t>C_0402</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>MLCC 100pF 50V C0G (comp)</t>
+          <t>MLCC 2.2pF 50V C0G 0402 (TIA feedback; CL05C2R2CB5NNNC obsolete)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1276-1014-2-ND</t>
+          <t>490-5932-2-ND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Samsung Electro-Mechanics</t>
+          <t>Murata Electronics</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>188189</v>
+        <v>308684</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
         <v>1</v>
@@ -3432,57 +3432,57 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/609/CL21C101JBANNNC_Spec.pdf</t>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8942/490_Chip_Multilayer_CAT2021_MLCC.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GRM1555C1H2R2CA01D</t>
+          <t>374144-E</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Murata Electronics</t>
+          <t>TE Connectivity AMP</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CH_Card C_f1,C_f2</t>
+          <t>CH_Card J1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2.2pF</t>
+          <t>DIN41612 M 3x8+8</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>C_0402</t>
+          <t>DIN41612_M_Power_Male</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>MLCC 2.2pF 50V C0G 0402 (TIA feedback; CL05C2R2CB5NNNC obsolete)</t>
+          <t>DIN41612 Type M 24sig+8pwr R/A male (same as pm6V/pm1p8V) - 0 STOCK, check lead time</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>490-5932-2-ND</t>
+          <t>2684-374144-E-ND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Murata Electronics</t>
+          <t>TE Connectivity Erni</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>308684</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1</v>
+        <v>10.31</v>
       </c>
       <c r="O42" s="4">
         <f>N42*L42</f>
@@ -3504,10 +3504,14 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8942/490_Chip_Multilayer_CAT2021_MLCC.pdf</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
+          <t>https://www.erni.com/fileadmin/import/products/assets/DC0006731.PDF</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>LOW STOCK (0 &lt; 1)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3515,46 +3519,46 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>374144-E</t>
+          <t>SFH11-PBPC-D07-ST-BK</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity AMP</t>
+          <t>Sullins Connector</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CH_Card J1</t>
+          <t>CH_Card J_BTF1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>DIN41612 M 3x8+8</t>
+          <t>2x7 socket</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>DIN41612_M_Power_Male</t>
+          <t>PinSocket_2x07</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>DIN41612 Type M 24sig+8pwr R/A male (same as pm6V/pm1p8V) - 0 STOCK, check lead time</t>
+          <t>Socket 2x7 2.54mm gold (butterfly laser; PPTC072LFBN-RC 0 stock)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2684-374144-E-ND</t>
+          <t>S9195-ND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TE Connectivity Erni</t>
+          <t>Sullins Connector Solutions</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>14015</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3568,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>10.31</v>
+        <v>0.8</v>
       </c>
       <c r="O43" s="4">
         <f>N43*L43</f>
@@ -3576,61 +3580,57 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://www.erni.com/fileadmin/import/products/assets/DC0006731.PDF</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>LOW STOCK (0 &lt; 1)</t>
-        </is>
-      </c>
+          <t>https://s3.amazonaws.com/catalogspreads-pdf/PAGE123%20.100%20SFH11%20SERIES%20FEMALE%20HDR%20ST%20RA.pdf</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SFH11-PBPC-D07-ST-BK</t>
+          <t>61300211121</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Sullins Connector</t>
+          <t>Wurth Elektronik</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CH_Card J_BTF1</t>
+          <t>CH_Card JP101,JP102,JP103</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2x7 socket</t>
+          <t>1x2 header</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_2x07</t>
+          <t>PinHeader_1x02</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Socket 2x7 2.54mm gold (butterfly laser; PPTC072LFBN-RC 0 stock)</t>
+          <t>Pin header 1x2 2.54mm (GA address jumpers)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>S9195-ND</t>
+          <t>732-5315-ND</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Sullins Connector Solutions</t>
+          <t>Würth Elektronik</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>14015</v>
+        <v>229019</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.8</v>
+        <v>0.13</v>
       </c>
       <c r="O44" s="4">
         <f>N44*L44</f>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://s3.amazonaws.com/catalogspreads-pdf/PAGE123%20.100%20SFH11%20SERIES%20FEMALE%20HDR%20ST%20RA.pdf</t>
+          <t>https://www.we-online.com/components/products/datasheet/61300211121.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
@@ -3663,46 +3663,46 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>61300211121</t>
+          <t>SPC02SYAN</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Wurth Elektronik</t>
+          <t>Sullins Connector</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CH_Card JP101,JP102,JP103</t>
+          <t>CH_Card JP101-103 shunts</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1x2 header</t>
+          <t>shunt</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>PinHeader_1x02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pin header 1x2 2.54mm (GA address jumpers)</t>
+          <t>Shorting jumper 2.54mm gold (fit = address bit 0)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>732-5315-ND</t>
+          <t>S9001-ND</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Würth Elektronik</t>
+          <t>Sullins Connector Solutions</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>229073</v>
+        <v>626294</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="O45" s="4">
         <f>N45*L45</f>
@@ -3724,57 +3724,57 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.we-online.com/components/products/datasheet/61300211121.pdf</t>
+          <t>https://drawings-pdf.s3.amazonaws.com/11134.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SPC02SYAN</t>
+          <t>657-10ABPE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Sullins Connector</t>
+          <t>Wakefield Thermal Solutions</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CH_Card JP101-103 shunts</t>
+          <t>CH_Card HS1,HS2,HS3,HS4</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>shunt</t>
+          <t>Heatsink TO-220 vert 1in</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TO-220-3_Vertical_HS657</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Shorting jumper 2.54mm gold (fit = address bit 0)</t>
+          <t>Vert board-mount heatsink 657-series 25.4mm, 6.8C/W nat (TEC H-bridge Q13/Q14/Q17/Q18; same as pm6V)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>S9001-ND</t>
+          <t>657-10ABPE-ND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sullins Connector Solutions</t>
+          <t>Wakefield Thermal Solutions</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>626394</v>
+        <v>1979</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3782,13 +3782,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1</v>
+        <v>2.49</v>
       </c>
       <c r="O46" s="4">
         <f>N46*L46</f>
@@ -3796,30 +3796,522 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://drawings-pdf.s3.amazonaws.com/11134.pdf</t>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/1883/Wakefield-657-15ABPE-datasheet.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
+      <c r="A47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>4880G</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Boyd</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card Q13,Q14,Q17,Q18 (TO-220 iso)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TO-220 mount kit</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Insulator+shoulder washer kit; isolates FET tab from heatsink (tabs are live: +6V_TEC / bridge outputs)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>HS417-ND</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Boyd Laconia, LLC</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>23841</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O47" s="4">
+        <f>N47*L47</f>
+        <v/>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://info.boydcorp.com/hubfs/Thermal/Air-Cooling/Boyd-Board-Level-Heatsinks-Catalog.pdf</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="N48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>PMSSS 440 0050 PH</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card Q13-Q18 heatsink mount</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>#4-40 x 1/2in screw</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>SS pan-head machine screw #4-40 x 1/2in (FET to 657 web)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>H705-ND</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>18371</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>4</v>
+      </c>
+      <c r="M48" t="n">
+        <v>100</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="O48" s="4">
+        <f>N48*L48</f>
+        <v/>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>FWSS 004</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card Q13-Q18 heatsink mount</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>#4 flat washer</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SS #4 flat washer, nut side</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>H734-ND</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>23941</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>4</v>
+      </c>
+      <c r="M49" t="n">
+        <v>100</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="O49" s="4">
+        <f>N49*L49</f>
+        <v/>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>INTLWZ 004</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card Q13-Q18 heatsink mount</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>#4 int-tooth lock washer</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Internal-tooth lock washer #4 (anti-rotation)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>H236-ND</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>15096</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>4</v>
+      </c>
+      <c r="M50" t="n">
+        <v>100</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="O50" s="4">
+        <f>N50*L50</f>
+        <v/>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8325/INTLWZ-004-Datasheet.pdf</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>HNZ 440</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card Q13-Q18 heatsink mount</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>#4-40 hex nut</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>#4-40 hex nut, zinc-plated steel</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>H216-ND</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>25539</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>100</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O51" s="4">
+        <f>N51*L51</f>
+        <v/>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>WSL2512R0100FEA</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Vishay Dale</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card R68,R76</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>10mR link</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>R_2512</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>0.01R 1% 1W 2512 - TEC drive links to butterfly (was 47R: blocked TEC current)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>WSLG-.01TR-ND</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Vishay Dale</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>111997</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O52" s="4">
+        <f>N52*L52</f>
+        <v/>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://www.vishay.com/docs/30100/wsl.pdf</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>RC0805JR-070RL</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>CH_Card R73,R74</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0R link</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>R_0805</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0R jumper - laser CHIP+/- links (was 47R: no laser headroom)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>311-0.0ARTR-ND</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>YAGEO</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1429677</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O53" s="4">
+        <f>N53*L53</f>
+        <v/>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="O48" s="5">
-        <f>SUM(O2:O46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Prices pulled 2026-07-17 12:44 (USD), 1 board(s)</t>
+      <c r="O55" s="5">
+        <f>SUM(O2:O53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Prices pulled 2026-07-17 14:21 (USD), 1 board(s)</t>
         </is>
       </c>
     </row>

--- a/Lasser_Driver_v5/CH_Card/CH_Card_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/CH_Card/CH_Card_BOM_digikey_priced.xlsx
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>46019</v>
+        <v>45981</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>25495</v>
+        <v>25223</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>117162</v>
+        <v>118154</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11659</v>
+        <v>11651</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1968</v>
+        <v>272</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>223661</v>
+        <v>222126</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3413350</v>
+        <v>3412222</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>197469</v>
+        <v>196894</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>224752</v>
+        <v>224742</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>855984</v>
+        <v>855781</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>249333</v>
+        <v>248558</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>170424</v>
+        <v>115448</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>108045</v>
+        <v>107890</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>384782</v>
+        <v>384532</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>19030</v>
+        <v>18975</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>7390781</v>
+        <v>7388655</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>139665</v>
+        <v>139705</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>212636</v>
+        <v>215184</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4559</v>
+        <v>3459</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2434788</v>
+        <v>2434279</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>40958</v>
+        <v>40908</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1394498</v>
+        <v>1389919</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>188189</v>
+        <v>188089</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SFH11-PBPC-D07-ST-BK</t>
+          <t>61301421121</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Sullins Connector</t>
+          <t>Würth Elektronik</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3534,31 +3534,31 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2x7 socket</t>
+          <t>2x7 pin header</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>PinSocket_2x07</t>
+          <t>PinHeader_2x07_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Socket 2x7 2.54mm gold (butterfly laser; PPTC072LFBN-RC 0 stock)</t>
+          <t>Würth WR-PHD 2.54mm 2x7 male pin header - board side of the off-board laser-head harness; same connector family as the LDM-BUTTERFLY mount socket (Würth 61301421821). Wire assembly (cable) sourced separately - spec 24AWG for the TEC pair.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>S9195-ND</t>
+          <t>732-5298-ND</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Sullins Connector Solutions</t>
+          <t>Würth Elektronik</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>14015</v>
+        <v>3911</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="O43" s="4">
         <f>N43*L43</f>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://s3.amazonaws.com/catalogspreads-pdf/PAGE123%20.100%20SFH11%20SERIES%20FEMALE%20HDR%20ST%20RA.pdf</t>
+          <t>https://www.we-online.com/catalog/datasheet/61301421121.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>229019</v>
+        <v>228427</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>626294</v>
+        <v>621810</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>23841</v>
+        <v>23829</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>15096</v>
+        <v>15296</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>111997</v>
+        <v>111995</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1429677</v>
+        <v>1428784</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
     <row r="56">
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Prices pulled 2026-07-17 14:21 (USD), 1 board(s)</t>
+          <t>Prices pulled 2026-07-19 16:04 (USD), 1 board(s)</t>
         </is>
       </c>
     </row>
